--- a/templates/three-statement-model.xlsx
+++ b/templates/three-statement-model.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="Rc93d9e574f0d45c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" r:id="R1adee7b2f12c4538"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income Statement" sheetId="3" r:id="R6546450f2c394a40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="4" r:id="R48b6c9105875462f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow" sheetId="5" r:id="R074c0641d6f84cde"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="6" r:id="R02cb0053cf8e4798"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="7" r:id="R1530fcddd9ce44a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="R4e0ab6953bc0461f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" r:id="Rbfcbe3ab4c6246d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income Statement" sheetId="3" r:id="Rfa41294f4a614682"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="4" r:id="Rcc914e35fc724765"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow" sheetId="5" r:id="Re97ecc3e152c4120"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="6" r:id="R69d58cfa218f4536"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="7" r:id="R8e864ffa3f184e97"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -203,7 +203,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="61">
+  <x:cellXfs count="72">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -305,6 +305,39 @@
     <x:xf numFmtId="204" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -316,7 +349,7 @@
         <x:color rgb="FF006100"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -327,7 +360,7 @@
         <x:color rgb="FF006100"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -338,7 +371,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -598,180 +631,181 @@
         <x:v>Modelo Integrado de Três Demonstrações — Atlas AI Brasil</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="12" t="str">
-        <x:v>Purpose</x:v>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="61" t="str">
+        <x:v>Objetivo</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
         <x:v>Template educacional para conectar P&amp;L, balanço e caixa em 24 meses.</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="13" t="str">
-        <x:v>Version</x:v>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="62" t="str">
+        <x:v>Versão</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
         <x:v>1.0</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="13" t="str">
-        <x:v>As of</x:v>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="62" t="str">
+        <x:v>Data de referência</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
         <x:v>2026-07-23</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="13" t="str">
-        <x:v>Currency / scale</x:v>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="62" t="str">
+        <x:v>Moeda / escala</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>BRL thousands</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="13" t="str">
-        <x:v>Forecast</x:v>
+        <x:v>R$ mil</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="62" t="str">
+        <x:v>Previsão</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>Jan-2026 to Dec-2027, monthly</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="13" t="str">
-        <x:v>Scenario</x:v>
+        <x:v>Jan/2026 a dez/2027, mensal</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="62" t="str">
+        <x:v>Cenário</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>Synthetic teaching case; not a real company forecast.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="13" t="str">
-        <x:v>Color convention</x:v>
+        <x:v>Caso didático sintético; não é previsão de empresa real.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="62" t="str">
+        <x:v>Convenção de cores</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>Blue font = input; black = formula; green = cross-sheet link.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="13" t="str">
-        <x:v>Model status</x:v>
+        <x:v>Azul: entrada; preto: fórmula; verde: vínculo entre abas.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="62" t="str">
+        <x:v>Situação do modelo</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>See Checks sheet. PASS means structural checks only.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="14" t="str">
-        <x:v>Use</x:v>
+        <x:v>Ver aba Checks. PASS indica somente verificações estruturais.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="63" t="str">
+        <x:v>Uso</x:v>
       </x:c>
       <x:c r="B12" s="11" t="str">
-        <x:v>Personal, private and non-commercial.</x:v>
-      </x:c>
-    </x:row>
+        <x:v>Material educacional público; preservar créditos e licença.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13"/>
     <x:row r="14">
       <x:c r="A14" s="17" t="str">
-        <x:v>WARNING: tax, revenue recognition and FX mechanics are simplified management assumptions. Real use requires controller, CFO and local tax/legal review.</x:v>
+        <x:v>Tributação, reconhecimento de receita e câmbio são simplificações gerenciais didáticas. Uso real exige revisão contábil, financeira e jurídica local.</x:v>
       </x:c>
       <x:c r="B14" s="17" t="str">
-        <x:v>WARNING: tax, revenue recognition and FX mechanics are simplified management assumptions. Real use requires controller, CFO and local tax/legal review.</x:v>
+        <x:v>Tributação, reconhecimento de receita e câmbio são simplificações gerenciais didáticas. Uso real exige revisão contábil, financeira e jurídica local.</x:v>
       </x:c>
       <x:c r="C14" s="17" t="str">
-        <x:v>WARNING: tax, revenue recognition and FX mechanics are simplified management assumptions. Real use requires controller, CFO and local tax/legal review.</x:v>
+        <x:v>Tributação, reconhecimento de receita e câmbio são simplificações gerenciais didáticas. Uso real exige revisão contábil, financeira e jurídica local.</x:v>
       </x:c>
       <x:c r="D14" s="17" t="str">
-        <x:v>WARNING: tax, revenue recognition and FX mechanics are simplified management assumptions. Real use requires controller, CFO and local tax/legal review.</x:v>
+        <x:v>Tributação, reconhecimento de receita e câmbio são simplificações gerenciais didáticas. Uso real exige revisão contábil, financeira e jurídica local.</x:v>
       </x:c>
       <x:c r="E14" s="17" t="str">
-        <x:v>WARNING: tax, revenue recognition and FX mechanics are simplified management assumptions. Real use requires controller, CFO and local tax/legal review.</x:v>
+        <x:v>Tributação, reconhecimento de receita e câmbio são simplificações gerenciais didáticas. Uso real exige revisão contábil, financeira e jurídica local.</x:v>
       </x:c>
       <x:c r="F14" s="17" t="str">
-        <x:v>WARNING: tax, revenue recognition and FX mechanics are simplified management assumptions. Real use requires controller, CFO and local tax/legal review.</x:v>
+        <x:v>Tributação, reconhecimento de receita e câmbio são simplificações gerenciais didáticas. Uso real exige revisão contábil, financeira e jurídica local.</x:v>
       </x:c>
       <x:c r="G14" s="17" t="str">
-        <x:v>WARNING: tax, revenue recognition and FX mechanics are simplified management assumptions. Real use requires controller, CFO and local tax/legal review.</x:v>
+        <x:v>Tributação, reconhecimento de receita e câmbio são simplificações gerenciais didáticas. Uso real exige revisão contábil, financeira e jurídica local.</x:v>
       </x:c>
       <x:c r="H14" s="17" t="str">
-        <x:v>WARNING: tax, revenue recognition and FX mechanics are simplified management assumptions. Real use requires controller, CFO and local tax/legal review.</x:v>
+        <x:v>Tributação, reconhecimento de receita e câmbio são simplificações gerenciais didáticas. Uso real exige revisão contábil, financeira e jurídica local.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="17" t="str">
-        <x:v>WARNING: tax, revenue recognition and FX mechanics are simplified management assumptions. Real use requires controller, CFO and local tax/legal review.</x:v>
+        <x:v>Tributação, reconhecimento de receita e câmbio são simplificações gerenciais didáticas. Uso real exige revisão contábil, financeira e jurídica local.</x:v>
       </x:c>
       <x:c r="B15" s="17" t="str">
-        <x:v>WARNING: tax, revenue recognition and FX mechanics are simplified management assumptions. Real use requires controller, CFO and local tax/legal review.</x:v>
+        <x:v>Tributação, reconhecimento de receita e câmbio são simplificações gerenciais didáticas. Uso real exige revisão contábil, financeira e jurídica local.</x:v>
       </x:c>
       <x:c r="C15" s="17" t="str">
-        <x:v>WARNING: tax, revenue recognition and FX mechanics are simplified management assumptions. Real use requires controller, CFO and local tax/legal review.</x:v>
+        <x:v>Tributação, reconhecimento de receita e câmbio são simplificações gerenciais didáticas. Uso real exige revisão contábil, financeira e jurídica local.</x:v>
       </x:c>
       <x:c r="D15" s="17" t="str">
-        <x:v>WARNING: tax, revenue recognition and FX mechanics are simplified management assumptions. Real use requires controller, CFO and local tax/legal review.</x:v>
+        <x:v>Tributação, reconhecimento de receita e câmbio são simplificações gerenciais didáticas. Uso real exige revisão contábil, financeira e jurídica local.</x:v>
       </x:c>
       <x:c r="E15" s="17" t="str">
-        <x:v>WARNING: tax, revenue recognition and FX mechanics are simplified management assumptions. Real use requires controller, CFO and local tax/legal review.</x:v>
+        <x:v>Tributação, reconhecimento de receita e câmbio são simplificações gerenciais didáticas. Uso real exige revisão contábil, financeira e jurídica local.</x:v>
       </x:c>
       <x:c r="F15" s="17" t="str">
-        <x:v>WARNING: tax, revenue recognition and FX mechanics are simplified management assumptions. Real use requires controller, CFO and local tax/legal review.</x:v>
+        <x:v>Tributação, reconhecimento de receita e câmbio são simplificações gerenciais didáticas. Uso real exige revisão contábil, financeira e jurídica local.</x:v>
       </x:c>
       <x:c r="G15" s="17" t="str">
-        <x:v>WARNING: tax, revenue recognition and FX mechanics are simplified management assumptions. Real use requires controller, CFO and local tax/legal review.</x:v>
+        <x:v>Tributação, reconhecimento de receita e câmbio são simplificações gerenciais didáticas. Uso real exige revisão contábil, financeira e jurídica local.</x:v>
       </x:c>
       <x:c r="H15" s="17" t="str">
-        <x:v>WARNING: tax, revenue recognition and FX mechanics are simplified management assumptions. Real use requires controller, CFO and local tax/legal review.</x:v>
+        <x:v>Tributação, reconhecimento de receita e câmbio são simplificações gerenciais didáticas. Uso real exige revisão contábil, financeira e jurídica local.</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="17" t="str">
-        <x:v>WARNING: tax, revenue recognition and FX mechanics are simplified management assumptions. Real use requires controller, CFO and local tax/legal review.</x:v>
+        <x:v>Tributação, reconhecimento de receita e câmbio são simplificações gerenciais didáticas. Uso real exige revisão contábil, financeira e jurídica local.</x:v>
       </x:c>
       <x:c r="B16" s="17" t="str">
-        <x:v>WARNING: tax, revenue recognition and FX mechanics are simplified management assumptions. Real use requires controller, CFO and local tax/legal review.</x:v>
+        <x:v>Tributação, reconhecimento de receita e câmbio são simplificações gerenciais didáticas. Uso real exige revisão contábil, financeira e jurídica local.</x:v>
       </x:c>
       <x:c r="C16" s="17" t="str">
-        <x:v>WARNING: tax, revenue recognition and FX mechanics are simplified management assumptions. Real use requires controller, CFO and local tax/legal review.</x:v>
+        <x:v>Tributação, reconhecimento de receita e câmbio são simplificações gerenciais didáticas. Uso real exige revisão contábil, financeira e jurídica local.</x:v>
       </x:c>
       <x:c r="D16" s="17" t="str">
-        <x:v>WARNING: tax, revenue recognition and FX mechanics are simplified management assumptions. Real use requires controller, CFO and local tax/legal review.</x:v>
+        <x:v>Tributação, reconhecimento de receita e câmbio são simplificações gerenciais didáticas. Uso real exige revisão contábil, financeira e jurídica local.</x:v>
       </x:c>
       <x:c r="E16" s="17" t="str">
-        <x:v>WARNING: tax, revenue recognition and FX mechanics are simplified management assumptions. Real use requires controller, CFO and local tax/legal review.</x:v>
+        <x:v>Tributação, reconhecimento de receita e câmbio são simplificações gerenciais didáticas. Uso real exige revisão contábil, financeira e jurídica local.</x:v>
       </x:c>
       <x:c r="F16" s="17" t="str">
-        <x:v>WARNING: tax, revenue recognition and FX mechanics are simplified management assumptions. Real use requires controller, CFO and local tax/legal review.</x:v>
+        <x:v>Tributação, reconhecimento de receita e câmbio são simplificações gerenciais didáticas. Uso real exige revisão contábil, financeira e jurídica local.</x:v>
       </x:c>
       <x:c r="G16" s="17" t="str">
-        <x:v>WARNING: tax, revenue recognition and FX mechanics are simplified management assumptions. Real use requires controller, CFO and local tax/legal review.</x:v>
+        <x:v>Tributação, reconhecimento de receita e câmbio são simplificações gerenciais didáticas. Uso real exige revisão contábil, financeira e jurídica local.</x:v>
       </x:c>
       <x:c r="H16" s="17" t="str">
-        <x:v>WARNING: tax, revenue recognition and FX mechanics are simplified management assumptions. Real use requires controller, CFO and local tax/legal review.</x:v>
+        <x:v>Tributação, reconhecimento de receita e câmbio são simplificações gerenciais didáticas. Uso real exige revisão contábil, financeira e jurídica local.</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="17" t="str">
-        <x:v>WARNING: tax, revenue recognition and FX mechanics are simplified management assumptions. Real use requires controller, CFO and local tax/legal review.</x:v>
+        <x:v>Tributação, reconhecimento de receita e câmbio são simplificações gerenciais didáticas. Uso real exige revisão contábil, financeira e jurídica local.</x:v>
       </x:c>
       <x:c r="B17" s="17" t="str">
-        <x:v>WARNING: tax, revenue recognition and FX mechanics are simplified management assumptions. Real use requires controller, CFO and local tax/legal review.</x:v>
+        <x:v>Tributação, reconhecimento de receita e câmbio são simplificações gerenciais didáticas. Uso real exige revisão contábil, financeira e jurídica local.</x:v>
       </x:c>
       <x:c r="C17" s="17" t="str">
-        <x:v>WARNING: tax, revenue recognition and FX mechanics are simplified management assumptions. Real use requires controller, CFO and local tax/legal review.</x:v>
+        <x:v>Tributação, reconhecimento de receita e câmbio são simplificações gerenciais didáticas. Uso real exige revisão contábil, financeira e jurídica local.</x:v>
       </x:c>
       <x:c r="D17" s="17" t="str">
-        <x:v>WARNING: tax, revenue recognition and FX mechanics are simplified management assumptions. Real use requires controller, CFO and local tax/legal review.</x:v>
+        <x:v>Tributação, reconhecimento de receita e câmbio são simplificações gerenciais didáticas. Uso real exige revisão contábil, financeira e jurídica local.</x:v>
       </x:c>
       <x:c r="E17" s="17" t="str">
-        <x:v>WARNING: tax, revenue recognition and FX mechanics are simplified management assumptions. Real use requires controller, CFO and local tax/legal review.</x:v>
+        <x:v>Tributação, reconhecimento de receita e câmbio são simplificações gerenciais didáticas. Uso real exige revisão contábil, financeira e jurídica local.</x:v>
       </x:c>
       <x:c r="F17" s="17" t="str">
-        <x:v>WARNING: tax, revenue recognition and FX mechanics are simplified management assumptions. Real use requires controller, CFO and local tax/legal review.</x:v>
+        <x:v>Tributação, reconhecimento de receita e câmbio são simplificações gerenciais didáticas. Uso real exige revisão contábil, financeira e jurídica local.</x:v>
       </x:c>
       <x:c r="G17" s="17" t="str">
-        <x:v>WARNING: tax, revenue recognition and FX mechanics are simplified management assumptions. Real use requires controller, CFO and local tax/legal review.</x:v>
+        <x:v>Tributação, reconhecimento de receita e câmbio são simplificações gerenciais didáticas. Uso real exige revisão contábil, financeira e jurídica local.</x:v>
       </x:c>
       <x:c r="H17" s="17" t="str">
-        <x:v>WARNING: tax, revenue recognition and FX mechanics are simplified management assumptions. Real use requires controller, CFO and local tax/legal review.</x:v>
+        <x:v>Tributação, reconhecimento de receita e câmbio são simplificações gerenciais didáticas. Uso real exige revisão contábil, financeira e jurídica local.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -795,161 +829,161 @@
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Assumptions</x:v>
+        <x:v>Premissas</x:v>
       </x:c>
       <x:c r="B1" s="3" t="str">
-        <x:v>Assumptions</x:v>
+        <x:v>Premissas</x:v>
       </x:c>
       <x:c r="C1" s="3" t="str">
-        <x:v>Assumptions</x:v>
+        <x:v>Premissas</x:v>
       </x:c>
       <x:c r="D1" s="3" t="str">
-        <x:v>Assumptions</x:v>
+        <x:v>Premissas</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>Assumptions</x:v>
+        <x:v>Premissas</x:v>
       </x:c>
       <x:c r="B2" s="3" t="str">
-        <x:v>Assumptions</x:v>
+        <x:v>Premissas</x:v>
       </x:c>
       <x:c r="C2" s="3" t="str">
-        <x:v>Assumptions</x:v>
+        <x:v>Premissas</x:v>
       </x:c>
       <x:c r="D2" s="3" t="str">
-        <x:v>Assumptions</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="23" t="str">
-        <x:v>Driver</x:v>
-      </x:c>
-      <x:c r="B4" s="24" t="str">
-        <x:v>Value</x:v>
-      </x:c>
-      <x:c r="C4" s="24" t="str">
-        <x:v>Unit</x:v>
-      </x:c>
-      <x:c r="D4" s="25" t="str">
-        <x:v>Source / note</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" t="str">
-        <x:v>Initial cash</x:v>
+        <x:v>Premissas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="64" t="str">
+        <x:v>Premissa</x:v>
+      </x:c>
+      <x:c r="B4" s="65" t="str">
+        <x:v>Valor</x:v>
+      </x:c>
+      <x:c r="C4" s="65" t="str">
+        <x:v>Unidade</x:v>
+      </x:c>
+      <x:c r="D4" s="66" t="str">
+        <x:v>Fonte / nota</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="5" t="str">
+        <x:v>Caixa inicial</x:v>
       </x:c>
       <x:c r="B5" s="30" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="C5" t="str">
-        <x:v>BRL k</x:v>
+      <x:c r="C5" s="5" t="str">
+        <x:v>R$ mil</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
-        <x:v>Synthetic input</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="str">
-        <x:v>Initial accounts receivable</x:v>
+        <x:v>Entrada sintética</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="5" t="str">
+        <x:v>Contas a receber iniciais</x:v>
       </x:c>
       <x:c r="B6" s="30" t="n">
         <x:v>500</x:v>
       </x:c>
-      <x:c r="C6" t="str">
-        <x:v>BRL k</x:v>
+      <x:c r="C6" s="5" t="str">
+        <x:v>R$ mil</x:v>
       </x:c>
       <x:c r="D6" s="5" t="str">
-        <x:v>Synthetic input</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="str">
-        <x:v>Initial accounts payable</x:v>
+        <x:v>Entrada sintética</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="5" t="str">
+        <x:v>Contas a pagar iniciais</x:v>
       </x:c>
       <x:c r="B7" s="30" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="C7" t="str">
-        <x:v>BRL k</x:v>
+      <x:c r="C7" s="5" t="str">
+        <x:v>R$ mil</x:v>
       </x:c>
       <x:c r="D7" s="5" t="str">
-        <x:v>Synthetic input</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" t="str">
-        <x:v>Initial deferred revenue</x:v>
+        <x:v>Entrada sintética</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="5" t="str">
+        <x:v>Receita diferida inicial</x:v>
       </x:c>
       <x:c r="B8" s="30" t="n">
         <x:v>1200</x:v>
       </x:c>
-      <x:c r="C8" t="str">
-        <x:v>BRL k</x:v>
+      <x:c r="C8" s="5" t="str">
+        <x:v>R$ mil</x:v>
       </x:c>
       <x:c r="D8" s="5" t="str">
-        <x:v>Synthetic input</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" t="str">
-        <x:v>Initial net PPE</x:v>
+        <x:v>Entrada sintética</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="5" t="str">
+        <x:v>Imobilizado líquido inicial</x:v>
       </x:c>
       <x:c r="B9" s="30" t="n">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="C9" t="str">
-        <x:v>BRL k</x:v>
+      <x:c r="C9" s="5" t="str">
+        <x:v>R$ mil</x:v>
       </x:c>
       <x:c r="D9" s="5" t="str">
-        <x:v>Synthetic input</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" t="str">
-        <x:v>Initial debt</x:v>
+        <x:v>Entrada sintética</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="5" t="str">
+        <x:v>Dívida inicial</x:v>
       </x:c>
       <x:c r="B10" s="30" t="n">
         <x:v>1000</x:v>
       </x:c>
-      <x:c r="C10" t="str">
-        <x:v>BRL k</x:v>
+      <x:c r="C10" s="5" t="str">
+        <x:v>R$ mil</x:v>
       </x:c>
       <x:c r="D10" s="5" t="str">
-        <x:v>Synthetic input</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" t="str">
-        <x:v>Initial contributed equity</x:v>
+        <x:v>Entrada sintética</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="5" t="str">
+        <x:v>Capital aportado inicial</x:v>
       </x:c>
       <x:c r="B11" s="30" t="n">
         <x:v>4200</x:v>
       </x:c>
-      <x:c r="C11" t="str">
-        <x:v>BRL k</x:v>
+      <x:c r="C11" s="5" t="str">
+        <x:v>R$ mil</x:v>
       </x:c>
       <x:c r="D11" s="5" t="str">
-        <x:v>Balances opening assets and liabilities</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" t="str">
-        <x:v>Month 1 billings</x:v>
+        <x:v>Reconcilia ativos e passivos iniciais</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="5" t="str">
+        <x:v>Faturamento do mês 1</x:v>
       </x:c>
       <x:c r="B12" s="30" t="n">
         <x:v>1200</x:v>
       </x:c>
-      <x:c r="C12" t="str">
-        <x:v>BRL k</x:v>
+      <x:c r="C12" s="5" t="str">
+        <x:v>R$ mil</x:v>
       </x:c>
       <x:c r="D12" s="5" t="str">
-        <x:v>Synthetic input</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" t="str">
-        <x:v>Monthly billings growth</x:v>
+        <x:v>Entrada sintética</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="5" t="str">
+        <x:v>Crescimento mensal do faturamento</x:v>
       </x:c>
       <x:c r="B13" s="31" t="n">
         <x:v>0.05</x:v>
@@ -958,26 +992,26 @@
         <x:v>%</x:v>
       </x:c>
       <x:c r="D13" s="5" t="str">
-        <x:v>Synthetic input</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" t="str">
-        <x:v>Recognition rate on available deferred</x:v>
+        <x:v>Entrada sintética</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A14" s="5" t="str">
+        <x:v>Taxa de reconhecimento da receita diferida disponível</x:v>
       </x:c>
       <x:c r="B14" s="31" t="n">
         <x:v>0.35</x:v>
       </x:c>
-      <x:c r="C14" t="str">
-        <x:v>% per month</x:v>
+      <x:c r="C14" s="5" t="str">
+        <x:v>% ao mês</x:v>
       </x:c>
       <x:c r="D14" s="5" t="str">
-        <x:v>Synthetic simplification</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" t="str">
-        <x:v>COGS as % of revenue</x:v>
+        <x:v>Simplificação sintética</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="5" t="str">
+        <x:v>Custo dos serviços como % da receita</x:v>
       </x:c>
       <x:c r="B15" s="31" t="n">
         <x:v>0.28</x:v>
@@ -986,110 +1020,110 @@
         <x:v>%</x:v>
       </x:c>
       <x:c r="D15" s="5" t="str">
-        <x:v>Synthetic input</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" t="str">
-        <x:v>Cash operating expenses</x:v>
+        <x:v>Entrada sintética</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="5" t="str">
+        <x:v>Despesas operacionais desembolsáveis</x:v>
       </x:c>
       <x:c r="B16" s="30" t="n">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="C16" t="str">
-        <x:v>BRL k / month</x:v>
+      <x:c r="C16" s="5" t="str">
+        <x:v>R$ mil / mês</x:v>
       </x:c>
       <x:c r="D16" s="5" t="str">
-        <x:v>Synthetic input</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" t="str">
-        <x:v>Monthly depreciation</x:v>
+        <x:v>Entrada sintética</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" s="5" t="str">
+        <x:v>Depreciação mensal</x:v>
       </x:c>
       <x:c r="B17" s="30" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C17" t="str">
-        <x:v>BRL k</x:v>
+      <x:c r="C17" s="5" t="str">
+        <x:v>R$ mil</x:v>
       </x:c>
       <x:c r="D17" s="5" t="str">
-        <x:v>Synthetic input</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" t="str">
-        <x:v>AR collection rate</x:v>
+        <x:v>Entrada sintética</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A18" s="5" t="str">
+        <x:v>Taxa de recebimento de contas</x:v>
       </x:c>
       <x:c r="B18" s="31" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="C18" t="str">
-        <x:v>% of opening AR + billings</x:v>
+      <x:c r="C18" s="5" t="str">
+        <x:v>% de contas a receber iniciais + faturamento</x:v>
       </x:c>
       <x:c r="D18" s="5" t="str">
-        <x:v>Synthetic simplification</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" t="str">
-        <x:v>AP payment rate</x:v>
+        <x:v>Simplificação sintética</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A19" s="5" t="str">
+        <x:v>Taxa de pagamento de contas</x:v>
       </x:c>
       <x:c r="B19" s="31" t="n">
         <x:v>0.75</x:v>
       </x:c>
-      <x:c r="C19" t="str">
-        <x:v>% of opening AP + new cash costs</x:v>
+      <x:c r="C19" s="5" t="str">
+        <x:v>% de contas a pagar iniciais + novos custos desembolsáveis</x:v>
       </x:c>
       <x:c r="D19" s="5" t="str">
-        <x:v>Synthetic simplification</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" t="str">
-        <x:v>Monthly capex</x:v>
+        <x:v>Simplificação sintética</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="15" hidden="0" customHeight="1">
+      <x:c r="A20" s="5" t="str">
+        <x:v>Investimento mensal em imobilizado</x:v>
       </x:c>
       <x:c r="B20" s="30" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C20" t="str">
-        <x:v>BRL k</x:v>
+      <x:c r="C20" s="5" t="str">
+        <x:v>R$ mil</x:v>
       </x:c>
       <x:c r="D20" s="5" t="str">
-        <x:v>Synthetic input</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" t="str">
-        <x:v>Monthly debt principal</x:v>
+        <x:v>Entrada sintética</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="15" hidden="0" customHeight="1">
+      <x:c r="A21" s="5" t="str">
+        <x:v>Principal mensal da dívida</x:v>
       </x:c>
       <x:c r="B21" s="30" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C21" t="str">
-        <x:v>BRL k</x:v>
+      <x:c r="C21" s="5" t="str">
+        <x:v>R$ mil</x:v>
       </x:c>
       <x:c r="D21" s="5" t="str">
-        <x:v>Synthetic input</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" t="str">
-        <x:v>Monthly interest</x:v>
+        <x:v>Entrada sintética</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="15" hidden="0" customHeight="1">
+      <x:c r="A22" s="5" t="str">
+        <x:v>Juros mensais</x:v>
       </x:c>
       <x:c r="B22" s="30" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C22" t="str">
-        <x:v>BRL k</x:v>
+      <x:c r="C22" s="5" t="str">
+        <x:v>R$ mil</x:v>
       </x:c>
       <x:c r="D22" s="5" t="str">
-        <x:v>Synthetic input</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" t="str">
-        <x:v>Management tax rate</x:v>
+        <x:v>Entrada sintética</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="15" hidden="0" customHeight="1">
+      <x:c r="A23" s="5" t="str">
+        <x:v>Alíquota gerencial didática</x:v>
       </x:c>
       <x:c r="B23" s="31" t="n">
         <x:v>0</x:v>
@@ -1098,26 +1132,27 @@
         <x:v>%</x:v>
       </x:c>
       <x:c r="D23" s="5" t="str">
-        <x:v>Not validated for real use</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="23" t="str">
-        <x:v>Funding event</x:v>
-      </x:c>
-      <x:c r="B25" s="24" t="str">
-        <x:v>Month</x:v>
-      </x:c>
-      <x:c r="C25" s="24" t="str">
-        <x:v>Amount BRL k</x:v>
-      </x:c>
-      <x:c r="D25" s="25" t="str">
-        <x:v>Treatment</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" t="str">
-        <x:v>HQ equity contribution</x:v>
+        <x:v>Não validado para uso real</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24"/>
+    <x:row r="25" ht="15" hidden="0" customHeight="1">
+      <x:c r="A25" s="64" t="str">
+        <x:v>Evento de financiamento</x:v>
+      </x:c>
+      <x:c r="B25" s="65" t="str">
+        <x:v>Mês</x:v>
+      </x:c>
+      <x:c r="C25" s="65" t="str">
+        <x:v>Valor em R$ mil</x:v>
+      </x:c>
+      <x:c r="D25" s="66" t="str">
+        <x:v>Tratamento</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="15" hidden="0" customHeight="1">
+      <x:c r="A26" s="5" t="str">
+        <x:v>Aporte de capital da matriz</x:v>
       </x:c>
       <x:c r="B26" s="34" t="n">
         <x:v>7</x:v>
@@ -1125,20 +1160,20 @@
       <x:c r="C26" s="34" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="D26" t="str">
-        <x:v>Financing cash flow and contributed equity</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" t="str">
-        <x:v>No other funding</x:v>
+      <x:c r="D26" s="5" t="str">
+        <x:v>Caixa de financiamento e capital aportado</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="15" hidden="0" customHeight="1">
+      <x:c r="A27" s="5" t="str">
+        <x:v>Sem outro financiamento</x:v>
       </x:c>
       <x:c r="B27" s="34"/>
       <x:c r="C27" s="34" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D27" t="str">
-        <x:v>Synthetic input</x:v>
+      <x:c r="D27" s="5" t="str">
+        <x:v>Entrada sintética</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1182,238 +1217,238 @@
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="B1" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="C1" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="D1" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="E1" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="F1" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="G1" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="H1" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="I1" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="J1" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="K1" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="L1" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="M1" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="N1" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="O1" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="P1" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="Q1" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="R1" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="S1" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="T1" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="U1" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="V1" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="W1" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="X1" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="Y1" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="B2" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="C2" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="D2" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="E2" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="F2" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="G2" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="H2" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="I2" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="J2" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="K2" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="L2" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="M2" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="N2" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="O2" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="P2" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="Q2" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="R2" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="S2" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="T2" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="U2" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="V2" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="W2" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="X2" s="3" t="str">
-        <x:v>Income Statement</x:v>
+        <x:v>Demonstração de resultado</x:v>
       </x:c>
       <x:c r="Y2" s="3" t="str">
-        <x:v>Income Statement</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="35" t="str">
-        <x:v>BRL thousands | monthly forecast | synthetic case</x:v>
-      </x:c>
-      <x:c r="B4" s="35" t="str">
-        <x:v>BRL thousands | monthly forecast | synthetic case</x:v>
-      </x:c>
-      <x:c r="C4" s="35" t="str">
-        <x:v>BRL thousands | monthly forecast | synthetic case</x:v>
-      </x:c>
-      <x:c r="D4" s="35" t="str">
-        <x:v>BRL thousands | monthly forecast | synthetic case</x:v>
-      </x:c>
-      <x:c r="E4" s="35" t="str">
-        <x:v>BRL thousands | monthly forecast | synthetic case</x:v>
-      </x:c>
-      <x:c r="F4" s="35" t="str">
-        <x:v>BRL thousands | monthly forecast | synthetic case</x:v>
-      </x:c>
-      <x:c r="G4" s="35" t="str">
-        <x:v>BRL thousands | monthly forecast | synthetic case</x:v>
-      </x:c>
-      <x:c r="H4" s="35" t="str">
-        <x:v>BRL thousands | monthly forecast | synthetic case</x:v>
-      </x:c>
-      <x:c r="I4" s="35" t="str">
-        <x:v>BRL thousands | monthly forecast | synthetic case</x:v>
-      </x:c>
-      <x:c r="J4" s="35" t="str">
-        <x:v>BRL thousands | monthly forecast | synthetic case</x:v>
-      </x:c>
-      <x:c r="K4" s="35" t="str">
-        <x:v>BRL thousands | monthly forecast | synthetic case</x:v>
-      </x:c>
-      <x:c r="L4" s="35" t="str">
-        <x:v>BRL thousands | monthly forecast | synthetic case</x:v>
-      </x:c>
-      <x:c r="M4" s="35" t="str">
-        <x:v>BRL thousands | monthly forecast | synthetic case</x:v>
-      </x:c>
-      <x:c r="N4" s="35" t="str">
-        <x:v>BRL thousands | monthly forecast | synthetic case</x:v>
-      </x:c>
-      <x:c r="O4" s="35" t="str">
-        <x:v>BRL thousands | monthly forecast | synthetic case</x:v>
-      </x:c>
-      <x:c r="P4" s="35" t="str">
-        <x:v>BRL thousands | monthly forecast | synthetic case</x:v>
-      </x:c>
-      <x:c r="Q4" s="35" t="str">
-        <x:v>BRL thousands | monthly forecast | synthetic case</x:v>
-      </x:c>
-      <x:c r="R4" s="35" t="str">
-        <x:v>BRL thousands | monthly forecast | synthetic case</x:v>
-      </x:c>
-      <x:c r="S4" s="35" t="str">
-        <x:v>BRL thousands | monthly forecast | synthetic case</x:v>
-      </x:c>
-      <x:c r="T4" s="35" t="str">
-        <x:v>BRL thousands | monthly forecast | synthetic case</x:v>
-      </x:c>
-      <x:c r="U4" s="35" t="str">
-        <x:v>BRL thousands | monthly forecast | synthetic case</x:v>
-      </x:c>
-      <x:c r="V4" s="35" t="str">
-        <x:v>BRL thousands | monthly forecast | synthetic case</x:v>
-      </x:c>
-      <x:c r="W4" s="35" t="str">
-        <x:v>BRL thousands | monthly forecast | synthetic case</x:v>
-      </x:c>
-      <x:c r="X4" s="35" t="str">
-        <x:v>BRL thousands | monthly forecast | synthetic case</x:v>
-      </x:c>
-      <x:c r="Y4" s="35" t="str">
-        <x:v>BRL thousands | monthly forecast | synthetic case</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="23" t="str">
-        <x:v>Line item</x:v>
+        <x:v>Demonstração de resultado</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="67" t="str">
+        <x:v>R$ mil | previsão mensal | caso sintético</x:v>
+      </x:c>
+      <x:c r="B4" s="67" t="str">
+        <x:v>R$ mil | previsão mensal | caso sintético</x:v>
+      </x:c>
+      <x:c r="C4" s="67" t="str">
+        <x:v>R$ mil | previsão mensal | caso sintético</x:v>
+      </x:c>
+      <x:c r="D4" s="67" t="str">
+        <x:v>R$ mil | previsão mensal | caso sintético</x:v>
+      </x:c>
+      <x:c r="E4" s="67" t="str">
+        <x:v>R$ mil | previsão mensal | caso sintético</x:v>
+      </x:c>
+      <x:c r="F4" s="67" t="str">
+        <x:v>R$ mil | previsão mensal | caso sintético</x:v>
+      </x:c>
+      <x:c r="G4" s="67" t="str">
+        <x:v>R$ mil | previsão mensal | caso sintético</x:v>
+      </x:c>
+      <x:c r="H4" s="67" t="str">
+        <x:v>R$ mil | previsão mensal | caso sintético</x:v>
+      </x:c>
+      <x:c r="I4" s="67" t="str">
+        <x:v>R$ mil | previsão mensal | caso sintético</x:v>
+      </x:c>
+      <x:c r="J4" s="67" t="str">
+        <x:v>R$ mil | previsão mensal | caso sintético</x:v>
+      </x:c>
+      <x:c r="K4" s="67" t="str">
+        <x:v>R$ mil | previsão mensal | caso sintético</x:v>
+      </x:c>
+      <x:c r="L4" s="67" t="str">
+        <x:v>R$ mil | previsão mensal | caso sintético</x:v>
+      </x:c>
+      <x:c r="M4" s="67" t="str">
+        <x:v>R$ mil | previsão mensal | caso sintético</x:v>
+      </x:c>
+      <x:c r="N4" s="67" t="str">
+        <x:v>R$ mil | previsão mensal | caso sintético</x:v>
+      </x:c>
+      <x:c r="O4" s="67" t="str">
+        <x:v>R$ mil | previsão mensal | caso sintético</x:v>
+      </x:c>
+      <x:c r="P4" s="67" t="str">
+        <x:v>R$ mil | previsão mensal | caso sintético</x:v>
+      </x:c>
+      <x:c r="Q4" s="67" t="str">
+        <x:v>R$ mil | previsão mensal | caso sintético</x:v>
+      </x:c>
+      <x:c r="R4" s="67" t="str">
+        <x:v>R$ mil | previsão mensal | caso sintético</x:v>
+      </x:c>
+      <x:c r="S4" s="67" t="str">
+        <x:v>R$ mil | previsão mensal | caso sintético</x:v>
+      </x:c>
+      <x:c r="T4" s="67" t="str">
+        <x:v>R$ mil | previsão mensal | caso sintético</x:v>
+      </x:c>
+      <x:c r="U4" s="67" t="str">
+        <x:v>R$ mil | previsão mensal | caso sintético</x:v>
+      </x:c>
+      <x:c r="V4" s="67" t="str">
+        <x:v>R$ mil | previsão mensal | caso sintético</x:v>
+      </x:c>
+      <x:c r="W4" s="67" t="str">
+        <x:v>R$ mil | previsão mensal | caso sintético</x:v>
+      </x:c>
+      <x:c r="X4" s="67" t="str">
+        <x:v>R$ mil | previsão mensal | caso sintético</x:v>
+      </x:c>
+      <x:c r="Y4" s="67" t="str">
+        <x:v>R$ mil | previsão mensal | caso sintético</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="64" t="str">
+        <x:v>Linha</x:v>
       </x:c>
       <x:c r="B5" s="42" t="n">
         <x:v>46023</x:v>
@@ -1488,9 +1523,10 @@
         <x:v>46722</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="45" t="str">
-        <x:v>Billings</x:v>
+    <x:row r="6"/>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="68" t="str">
+        <x:v>Faturamento</x:v>
       </x:c>
       <x:c r="B7" s="47" t="n">
         <x:f>'Assumptions'!$B$12</x:f>
@@ -1589,9 +1625,9 @@
         <x:v>3685.828507101375</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="45" t="str">
-        <x:v>Revenue</x:v>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="68" t="str">
+        <x:v>Receita</x:v>
       </x:c>
       <x:c r="B8" s="47" t="n">
         <x:f>('Assumptions'!$B$8+B7)*'Assumptions'!$B$14</x:f>
@@ -1690,9 +1726,9 @@
         <x:v>3386.341875084213</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="45" t="str">
-        <x:v>COGS</x:v>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="68" t="str">
+        <x:v>Custo dos serviços</x:v>
       </x:c>
       <x:c r="B9" s="47" t="n">
         <x:f>-B8*'Assumptions'!$B$15</x:f>
@@ -1791,9 +1827,9 @@
         <x:v>-948.1757250235797</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="51" t="str">
-        <x:v>Gross profit</x:v>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="69" t="str">
+        <x:v>Lucro bruto</x:v>
       </x:c>
       <x:c r="B10" s="52" t="n">
         <x:f>SUM(B8:B9)</x:f>
@@ -1892,9 +1928,9 @@
         <x:v>2438.1661500606333</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="45" t="str">
-        <x:v>Gross margin</x:v>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="68" t="str">
+        <x:v>Margem bruta</x:v>
       </x:c>
       <x:c r="B11" s="48" t="n">
         <x:f>IF(B8=0,0,B10/B8)</x:f>
@@ -1993,9 +2029,9 @@
         <x:v>0.72</x:v>
       </x:c>
     </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="45" t="str">
-        <x:v>Cash operating expenses</x:v>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="68" t="str">
+        <x:v>Despesas operacionais desembolsáveis</x:v>
       </x:c>
       <x:c r="B12" s="47" t="n">
         <x:f>-'Assumptions'!$B$16</x:f>
@@ -2094,9 +2130,9 @@
         <x:v>-650</x:v>
       </x:c>
     </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="45" t="str">
-        <x:v>Depreciation &amp; amortization</x:v>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="68" t="str">
+        <x:v>Depreciação e amortização</x:v>
       </x:c>
       <x:c r="B13" s="47" t="n">
         <x:f>-'Assumptions'!$B$17</x:f>
@@ -2195,9 +2231,9 @@
         <x:v>-20</x:v>
       </x:c>
     </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="51" t="str">
-        <x:v>Operating income</x:v>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="69" t="str">
+        <x:v>Resultado operacional</x:v>
       </x:c>
       <x:c r="B14" s="52" t="n">
         <x:f>SUM(B10,B12:B13)</x:f>
@@ -2296,9 +2332,9 @@
         <x:v>1768.1661500606333</x:v>
       </x:c>
     </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="45" t="str">
-        <x:v>Operating margin</x:v>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="68" t="str">
+        <x:v>Margem operacional</x:v>
       </x:c>
       <x:c r="B15" s="48" t="n">
         <x:f>IF(B8=0,0,B14/B8)</x:f>
@@ -2397,9 +2433,9 @@
         <x:v>0.522146379569742</x:v>
       </x:c>
     </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="45" t="str">
-        <x:v>Interest expense</x:v>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="68" t="str">
+        <x:v>Despesa de juros</x:v>
       </x:c>
       <x:c r="B16" s="47" t="n">
         <x:f>-'Assumptions'!$B$22</x:f>
@@ -2498,9 +2534,9 @@
         <x:v>-10</x:v>
       </x:c>
     </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="45" t="str">
-        <x:v>Pre-tax income</x:v>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" s="68" t="str">
+        <x:v>Resultado antes de tributos</x:v>
       </x:c>
       <x:c r="B17" s="47" t="n">
         <x:f>SUM(B14,B16)</x:f>
@@ -2599,9 +2635,9 @@
         <x:v>1758.1661500606333</x:v>
       </x:c>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="45" t="str">
-        <x:v>Management tax</x:v>
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
+      <x:c r="A18" s="68" t="str">
+        <x:v>Tributo gerencial didático</x:v>
       </x:c>
       <x:c r="B18" s="47" t="n">
         <x:f>-MAX(0,B17*'Assumptions'!$B$23)</x:f>
@@ -2700,9 +2736,9 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="51" t="str">
-        <x:v>Net income</x:v>
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
+      <x:c r="A19" s="69" t="str">
+        <x:v>Lucro líquido</x:v>
       </x:c>
       <x:c r="B19" s="52" t="n">
         <x:f>SUM(B17:B18)</x:f>
@@ -2843,161 +2879,161 @@
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="B1" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="C1" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="D1" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="E1" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="F1" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="G1" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="H1" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="I1" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="J1" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="K1" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="L1" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="M1" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="N1" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="O1" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="P1" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="Q1" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="R1" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="S1" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="T1" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="U1" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="V1" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="W1" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="X1" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="Y1" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="B2" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="C2" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="D2" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="E2" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="F2" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="G2" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="H2" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="I2" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="J2" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="K2" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="L2" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="M2" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="N2" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="O2" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="P2" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="Q2" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="R2" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="S2" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="T2" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="U2" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="V2" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="W2" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="X2" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
+        <x:v>Balanço patrimonial</x:v>
       </x:c>
       <x:c r="Y2" s="3" t="str">
-        <x:v>Balance Sheet</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="23" t="str">
-        <x:v>Line item</x:v>
+        <x:v>Balanço patrimonial</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="64" t="str">
+        <x:v>Linha</x:v>
       </x:c>
       <x:c r="B4" s="42" t="n">
         <x:v>46023</x:v>
@@ -3072,9 +3108,10 @@
         <x:v>46722</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="str">
-        <x:v>Cash</x:v>
+    <x:row r="5"/>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="5" t="str">
+        <x:v>Caixa</x:v>
       </x:c>
       <x:c r="B6" s="47" t="n">
         <x:f>'Cash Flow'!B20</x:f>
@@ -3173,9 +3210,9 @@
         <x:v>32254.36337005929</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="str">
-        <x:v>Accounts receivable</x:v>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="5" t="str">
+        <x:v>Contas a receber</x:v>
       </x:c>
       <x:c r="B7" s="47" t="n">
         <x:f>'Assumptions'!$B$6+'Income Statement'!B7-('Assumptions'!$B$6+'Income Statement'!B7)*'Assumptions'!$B$18</x:f>
@@ -3274,9 +3311,9 @@
         <x:v>1548.0479729825834</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8" t="str">
-        <x:v>Net PPE</x:v>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="5" t="str">
+        <x:v>Imobilizado líquido</x:v>
       </x:c>
       <x:c r="B8" s="47" t="n">
         <x:f>'Assumptions'!$B$9+'Assumptions'!$B$20+'Income Statement'!B13</x:f>
@@ -3375,9 +3412,9 @@
         <x:v>680</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="54" t="str">
-        <x:v>Total assets</x:v>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="70" t="str">
+        <x:v>Ativos totais</x:v>
       </x:c>
       <x:c r="B9" s="52" t="n">
         <x:f>SUM(B6:B8)</x:f>
@@ -3476,9 +3513,9 @@
         <x:v>34482.41134304187</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
-      <x:c r="A10" t="str">
-        <x:v>Deferred revenue</x:v>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="5" t="str">
+        <x:v>Receita diferida</x:v>
       </x:c>
       <x:c r="B10" s="47" t="n">
         <x:f>'Assumptions'!$B$8+'Income Statement'!B7-'Income Statement'!B8</x:f>
@@ -3577,9 +3614,9 @@
         <x:v>6288.920625156396</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
-      <x:c r="A11" t="str">
-        <x:v>Accounts payable</x:v>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="5" t="str">
+        <x:v>Contas a pagar</x:v>
       </x:c>
       <x:c r="B11" s="47" t="n">
         <x:f>'Assumptions'!$B$7-'Income Statement'!B9-'Income Statement'!B12-('Assumptions'!$B$7-'Income Statement'!B9-'Income Statement'!B12)*'Assumptions'!$B$19</x:f>
@@ -3678,9 +3715,9 @@
         <x:v>527.7865406253218</x:v>
       </x:c>
     </x:row>
-    <x:row r="12">
-      <x:c r="A12" t="str">
-        <x:v>Debt</x:v>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="5" t="str">
+        <x:v>Dívida</x:v>
       </x:c>
       <x:c r="B12" s="47" t="n">
         <x:f>MAX(0,'Assumptions'!$B$10-'Assumptions'!$B$21)</x:f>
@@ -3779,9 +3816,9 @@
         <x:v>1000</x:v>
       </x:c>
     </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="54" t="str">
-        <x:v>Total liabilities</x:v>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="70" t="str">
+        <x:v>Passivos totais</x:v>
       </x:c>
       <x:c r="B13" s="52" t="n">
         <x:f>SUM(B10:B12)</x:f>
@@ -3880,9 +3917,9 @@
         <x:v>7816.707165781718</x:v>
       </x:c>
     </x:row>
-    <x:row r="14">
-      <x:c r="A14" t="str">
-        <x:v>Contributed equity</x:v>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="5" t="str">
+        <x:v>Capital aportado</x:v>
       </x:c>
       <x:c r="B14" s="47" t="n">
         <x:f>'Assumptions'!$B$11+SUM('Cash Flow'!$B$15:B15)</x:f>
@@ -3981,9 +4018,9 @@
         <x:v>8200</x:v>
       </x:c>
     </x:row>
-    <x:row r="15">
-      <x:c r="A15" t="str">
-        <x:v>Retained earnings</x:v>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="5" t="str">
+        <x:v>Lucros acumulados</x:v>
       </x:c>
       <x:c r="B15" s="47" t="n">
         <x:f>SUM('Income Statement'!$B$19:B19)</x:f>
@@ -4082,9 +4119,9 @@
         <x:v>18465.70417726015</x:v>
       </x:c>
     </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="54" t="str">
-        <x:v>Total equity</x:v>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="70" t="str">
+        <x:v>Patrimônio líquido total</x:v>
       </x:c>
       <x:c r="B16" s="52" t="n">
         <x:f>SUM(B14:B15)</x:f>
@@ -4183,9 +4220,9 @@
         <x:v>26665.70417726015</x:v>
       </x:c>
     </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="54" t="str">
-        <x:v>Liabilities + equity</x:v>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" s="70" t="str">
+        <x:v>Passivos + patrimônio líquido</x:v>
       </x:c>
       <x:c r="B17" s="52" t="n">
         <x:f>SUM(B13,B16)</x:f>
@@ -4284,9 +4321,9 @@
         <x:v>34482.411343041866</x:v>
       </x:c>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="55" t="str">
-        <x:v>Balance check</x:v>
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
+      <x:c r="A18" s="71" t="str">
+        <x:v>Conferência do balanço</x:v>
       </x:c>
       <x:c r="B18" s="56" t="n">
         <x:f>B9-B17</x:f>
@@ -4426,161 +4463,161 @@
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="B1" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="C1" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="D1" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="E1" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="F1" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="G1" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="H1" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="I1" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="J1" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="K1" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="L1" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="M1" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="N1" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="O1" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="P1" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="Q1" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="R1" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="S1" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="T1" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="U1" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="V1" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="W1" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="X1" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="Y1" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="B2" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="C2" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="D2" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="E2" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="F2" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="G2" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="H2" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="I2" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="J2" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="K2" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="L2" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="M2" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="N2" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="O2" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="P2" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="Q2" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="R2" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="S2" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="T2" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="U2" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="V2" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="W2" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="X2" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
       </x:c>
       <x:c r="Y2" s="3" t="str">
-        <x:v>Cash Flow Statement</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="23" t="str">
-        <x:v>Line item</x:v>
+        <x:v>Demonstração de fluxo de caixa</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="64" t="str">
+        <x:v>Linha</x:v>
       </x:c>
       <x:c r="B4" s="42" t="n">
         <x:v>46023</x:v>
@@ -4655,9 +4692,10 @@
         <x:v>46722</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="str">
-        <x:v>Net income</x:v>
+    <x:row r="5"/>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="5" t="str">
+        <x:v>Lucro líquido</x:v>
       </x:c>
       <x:c r="B6" s="47" t="n">
         <x:f>'Income Statement'!B19</x:f>
@@ -4756,7 +4794,7 @@
         <x:v>1758.1661500606333</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" t="str">
         <x:v>D&amp;A</x:v>
       </x:c>
@@ -4857,9 +4895,9 @@
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8" t="str">
-        <x:v>Change in accounts receivable</x:v>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="5" t="str">
+        <x:v>Variação em contas a receber</x:v>
       </x:c>
       <x:c r="B8" s="47" t="n">
         <x:f>-('Balance Sheet'!B7-'Assumptions'!$B$6)</x:f>
@@ -4958,9 +4996,9 @@
         <x:v>-73.71657014201446</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
-      <x:c r="A9" t="str">
-        <x:v>Change in deferred revenue</x:v>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="5" t="str">
+        <x:v>Variação em receita diferida</x:v>
       </x:c>
       <x:c r="B9" s="47" t="n">
         <x:f>'Balance Sheet'!B10-'Assumptions'!$B$8</x:f>
@@ -5059,9 +5097,9 @@
         <x:v>299.4866320171632</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
-      <x:c r="A10" t="str">
-        <x:v>Change in accounts payable</x:v>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="5" t="str">
+        <x:v>Variação em contas a pagar</x:v>
       </x:c>
       <x:c r="B10" s="47" t="n">
         <x:f>'Balance Sheet'!B11-'Assumptions'!$B$7</x:f>
@@ -5160,9 +5198,9 @@
         <x:v>14.81610314761383</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="54" t="str">
-        <x:v>Cash flow from operations</x:v>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="70" t="str">
+        <x:v>Caixa das operações</x:v>
       </x:c>
       <x:c r="B11" s="52" t="n">
         <x:f>SUM(B6:B10)</x:f>
@@ -5261,9 +5299,9 @@
         <x:v>2018.7523150833958</x:v>
       </x:c>
     </x:row>
-    <x:row r="12">
-      <x:c r="A12" t="str">
-        <x:v>Capital expenditure</x:v>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="5" t="str">
+        <x:v>Investimento em imobilizado</x:v>
       </x:c>
       <x:c r="B12" s="47" t="n">
         <x:f>-'Assumptions'!$B$20</x:f>
@@ -5362,9 +5400,9 @@
         <x:v>-40</x:v>
       </x:c>
     </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="54" t="str">
-        <x:v>Cash flow from investing</x:v>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="70" t="str">
+        <x:v>Caixa dos investimentos</x:v>
       </x:c>
       <x:c r="B13" s="52" t="n">
         <x:f>B12</x:f>
@@ -5463,9 +5501,9 @@
         <x:v>-40</x:v>
       </x:c>
     </x:row>
-    <x:row r="14">
-      <x:c r="A14" t="str">
-        <x:v>Debt principal</x:v>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="5" t="str">
+        <x:v>Principal da dívida</x:v>
       </x:c>
       <x:c r="B14" s="47" t="n">
         <x:f>-'Assumptions'!$B$21</x:f>
@@ -5564,9 +5602,9 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="15">
-      <x:c r="A15" t="str">
-        <x:v>HQ equity funding</x:v>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="5" t="str">
+        <x:v>Aporte de capital da matriz</x:v>
       </x:c>
       <x:c r="B15" s="47" t="n">
         <x:f>IF(COLUMN()-1='Assumptions'!$B$26,'Assumptions'!$C$26,0)</x:f>
@@ -5665,9 +5703,9 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="54" t="str">
-        <x:v>Cash flow from financing</x:v>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="70" t="str">
+        <x:v>Caixa dos financiamentos</x:v>
       </x:c>
       <x:c r="B16" s="52" t="n">
         <x:f>SUM(B14:B15)</x:f>
@@ -5766,9 +5804,9 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="17">
-      <x:c r="A17" t="str">
-        <x:v>FX effect</x:v>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" s="5" t="str">
+        <x:v>Efeito cambial</x:v>
       </x:c>
       <x:c r="B17" s="30" t="n">
         <x:v>0</x:v>
@@ -5843,9 +5881,9 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="54" t="str">
-        <x:v>Net change in cash</x:v>
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
+      <x:c r="A18" s="70" t="str">
+        <x:v>Variação líquida de caixa</x:v>
       </x:c>
       <x:c r="B18" s="52" t="n">
         <x:f>SUM(B11,B13,B16:B17)</x:f>
@@ -5944,9 +5982,9 @@
         <x:v>1978.7523150833958</x:v>
       </x:c>
     </x:row>
-    <x:row r="19">
-      <x:c r="A19" t="str">
-        <x:v>Beginning cash</x:v>
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
+      <x:c r="A19" s="5" t="str">
+        <x:v>Caixa inicial</x:v>
       </x:c>
       <x:c r="B19" s="57" t="n">
         <x:f>'Assumptions'!$B$5</x:f>
@@ -6045,9 +6083,9 @@
         <x:v>30275.611054975896</x:v>
       </x:c>
     </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="54" t="str">
-        <x:v>Ending cash</x:v>
+    <x:row r="20" ht="15" hidden="0" customHeight="1">
+      <x:c r="A20" s="70" t="str">
+        <x:v>Caixa final</x:v>
       </x:c>
       <x:c r="B20" s="52" t="n">
         <x:f>SUM(B18:B19)</x:f>
@@ -6169,76 +6207,76 @@
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Checks</x:v>
+        <x:v>Verificações</x:v>
       </x:c>
       <x:c r="B1" s="3" t="str">
-        <x:v>Checks</x:v>
+        <x:v>Verificações</x:v>
       </x:c>
       <x:c r="C1" s="3" t="str">
-        <x:v>Checks</x:v>
+        <x:v>Verificações</x:v>
       </x:c>
       <x:c r="D1" s="3" t="str">
-        <x:v>Checks</x:v>
+        <x:v>Verificações</x:v>
       </x:c>
       <x:c r="E1" s="3" t="str">
-        <x:v>Checks</x:v>
+        <x:v>Verificações</x:v>
       </x:c>
       <x:c r="F1" s="3" t="str">
-        <x:v>Checks</x:v>
+        <x:v>Verificações</x:v>
       </x:c>
       <x:c r="G1" s="3" t="str">
-        <x:v>Checks</x:v>
+        <x:v>Verificações</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>Checks</x:v>
+        <x:v>Verificações</x:v>
       </x:c>
       <x:c r="B2" s="3" t="str">
-        <x:v>Checks</x:v>
+        <x:v>Verificações</x:v>
       </x:c>
       <x:c r="C2" s="3" t="str">
-        <x:v>Checks</x:v>
+        <x:v>Verificações</x:v>
       </x:c>
       <x:c r="D2" s="3" t="str">
-        <x:v>Checks</x:v>
+        <x:v>Verificações</x:v>
       </x:c>
       <x:c r="E2" s="3" t="str">
-        <x:v>Checks</x:v>
+        <x:v>Verificações</x:v>
       </x:c>
       <x:c r="F2" s="3" t="str">
-        <x:v>Checks</x:v>
+        <x:v>Verificações</x:v>
       </x:c>
       <x:c r="G2" s="3" t="str">
-        <x:v>Checks</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="23" t="str">
-        <x:v>Check</x:v>
-      </x:c>
-      <x:c r="B4" s="24" t="str">
-        <x:v>Actual</x:v>
-      </x:c>
-      <x:c r="C4" s="24" t="str">
-        <x:v>Expected</x:v>
-      </x:c>
-      <x:c r="D4" s="24" t="str">
-        <x:v>Difference</x:v>
-      </x:c>
-      <x:c r="E4" s="24" t="str">
-        <x:v>Tolerance</x:v>
-      </x:c>
-      <x:c r="F4" s="24" t="str">
-        <x:v>Status</x:v>
-      </x:c>
-      <x:c r="G4" s="25" t="str">
-        <x:v>Where to fix</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" t="str">
-        <x:v>Balance sheet balances in final month</x:v>
+        <x:v>Verificações</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="64" t="str">
+        <x:v>Verificação</x:v>
+      </x:c>
+      <x:c r="B4" s="65" t="str">
+        <x:v>Realizado</x:v>
+      </x:c>
+      <x:c r="C4" s="65" t="str">
+        <x:v>Esperado</x:v>
+      </x:c>
+      <x:c r="D4" s="65" t="str">
+        <x:v>Diferença</x:v>
+      </x:c>
+      <x:c r="E4" s="65" t="str">
+        <x:v>Tolerância</x:v>
+      </x:c>
+      <x:c r="F4" s="65" t="str">
+        <x:v>Situação</x:v>
+      </x:c>
+      <x:c r="G4" s="66" t="str">
+        <x:v>Onde corrigir</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="5" t="str">
+        <x:v>Balanço fecha no mês final</x:v>
       </x:c>
       <x:c r="B5" s="58" t="n">
         <x:f>'Balance Sheet'!Y18</x:f>
@@ -6262,9 +6300,9 @@
         <x:v>Balance Sheet rows 6:17</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="str">
-        <x:v>Ending cash ties</x:v>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="5" t="str">
+        <x:v>Caixa final reconciliado</x:v>
       </x:c>
       <x:c r="B6" s="58" t="n">
         <x:f>'Balance Sheet'!Y6</x:f>
@@ -6289,9 +6327,9 @@
         <x:v>Cash Flow row 20</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="str">
-        <x:v>PPE roll-forward</x:v>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="5" t="str">
+        <x:v>Movimentação do imobilizado</x:v>
       </x:c>
       <x:c r="B7" s="58" t="n">
         <x:f>'Balance Sheet'!Y8</x:f>
@@ -6316,9 +6354,9 @@
         <x:v>Balance Sheet row 8</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8" t="str">
-        <x:v>Debt non-negative</x:v>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="5" t="str">
+        <x:v>Dívida não negativa</x:v>
       </x:c>
       <x:c r="B8" s="58" t="n">
         <x:f>MIN('Balance Sheet'!B12:Y12)</x:f>
@@ -6338,13 +6376,13 @@
         <x:f>IF(B8&gt;=0,"OK","FAIL")</x:f>
         <x:v>OK</x:v>
       </x:c>
-      <x:c r="G8" t="str">
-        <x:v>Assumptions / debt schedule</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" t="str">
-        <x:v>Deferred revenue non-negative</x:v>
+      <x:c r="G8" s="5" t="str">
+        <x:v>Premissas / cronograma de dívida</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A9" s="5" t="str">
+        <x:v>Receita diferida não negativa</x:v>
       </x:c>
       <x:c r="B9" s="58" t="n">
         <x:f>MIN('Balance Sheet'!B10:Y10)</x:f>
@@ -6364,13 +6402,13 @@
         <x:f>IF(B9&gt;=0,"OK","FAIL")</x:f>
         <x:v>OK</x:v>
       </x:c>
-      <x:c r="G9" t="str">
-        <x:v>Revenue recognition assumptions</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="35" t="str">
-        <x:v>MODEL STATUS</x:v>
+      <x:c r="G9" s="5" t="str">
+        <x:v>Premissas de reconhecimento de receita</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="67" t="str">
+        <x:v>SITUAÇÃO DO MODELO</x:v>
       </x:c>
       <x:c r="B10" s="35"/>
       <x:c r="C10" s="35"/>
@@ -6380,8 +6418,8 @@
         <x:f>IF(COUNTIF(F5:F9,"FAIL")=0,"PASS","FAIL")</x:f>
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="G10" s="35" t="str">
-        <x:v>All required checks</x:v>
+      <x:c r="G10" s="67" t="str">
+        <x:v>Todas as verificações obrigatórias</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6415,103 +6453,103 @@
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Sources / Audit</x:v>
+        <x:v>Fontes / auditoria</x:v>
       </x:c>
       <x:c r="B1" s="3" t="str">
-        <x:v>Sources / Audit</x:v>
+        <x:v>Fontes / auditoria</x:v>
       </x:c>
       <x:c r="C1" s="3" t="str">
-        <x:v>Sources / Audit</x:v>
+        <x:v>Fontes / auditoria</x:v>
       </x:c>
       <x:c r="D1" s="3" t="str">
-        <x:v>Sources / Audit</x:v>
+        <x:v>Fontes / auditoria</x:v>
       </x:c>
       <x:c r="E1" s="3" t="str">
-        <x:v>Sources / Audit</x:v>
+        <x:v>Fontes / auditoria</x:v>
       </x:c>
       <x:c r="F1" s="3" t="str">
-        <x:v>Sources / Audit</x:v>
+        <x:v>Fontes / auditoria</x:v>
       </x:c>
       <x:c r="G1" s="3" t="str">
-        <x:v>Sources / Audit</x:v>
+        <x:v>Fontes / auditoria</x:v>
       </x:c>
       <x:c r="H1" s="3" t="str">
-        <x:v>Sources / Audit</x:v>
+        <x:v>Fontes / auditoria</x:v>
       </x:c>
       <x:c r="I1" s="3" t="str">
-        <x:v>Sources / Audit</x:v>
+        <x:v>Fontes / auditoria</x:v>
       </x:c>
       <x:c r="J1" s="3" t="str">
-        <x:v>Sources / Audit</x:v>
+        <x:v>Fontes / auditoria</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>Sources / Audit</x:v>
+        <x:v>Fontes / auditoria</x:v>
       </x:c>
       <x:c r="B2" s="3" t="str">
-        <x:v>Sources / Audit</x:v>
+        <x:v>Fontes / auditoria</x:v>
       </x:c>
       <x:c r="C2" s="3" t="str">
-        <x:v>Sources / Audit</x:v>
+        <x:v>Fontes / auditoria</x:v>
       </x:c>
       <x:c r="D2" s="3" t="str">
-        <x:v>Sources / Audit</x:v>
+        <x:v>Fontes / auditoria</x:v>
       </x:c>
       <x:c r="E2" s="3" t="str">
-        <x:v>Sources / Audit</x:v>
+        <x:v>Fontes / auditoria</x:v>
       </x:c>
       <x:c r="F2" s="3" t="str">
-        <x:v>Sources / Audit</x:v>
+        <x:v>Fontes / auditoria</x:v>
       </x:c>
       <x:c r="G2" s="3" t="str">
-        <x:v>Sources / Audit</x:v>
+        <x:v>Fontes / auditoria</x:v>
       </x:c>
       <x:c r="H2" s="3" t="str">
-        <x:v>Sources / Audit</x:v>
+        <x:v>Fontes / auditoria</x:v>
       </x:c>
       <x:c r="I2" s="3" t="str">
-        <x:v>Sources / Audit</x:v>
+        <x:v>Fontes / auditoria</x:v>
       </x:c>
       <x:c r="J2" s="3" t="str">
-        <x:v>Sources / Audit</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
+        <x:v>Fontes / auditoria</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A4" s="23" t="str">
         <x:v>Item</x:v>
       </x:c>
-      <x:c r="B4" s="24" t="str">
-        <x:v>Value</x:v>
-      </x:c>
-      <x:c r="C4" s="24" t="str">
-        <x:v>Units</x:v>
-      </x:c>
-      <x:c r="D4" s="24" t="str">
-        <x:v>Period / as-of</x:v>
-      </x:c>
-      <x:c r="E4" s="24" t="str">
-        <x:v>Source type</x:v>
-      </x:c>
-      <x:c r="F4" s="24" t="str">
-        <x:v>Source name</x:v>
+      <x:c r="B4" s="65" t="str">
+        <x:v>Valor</x:v>
+      </x:c>
+      <x:c r="C4" s="65" t="str">
+        <x:v>Unidades</x:v>
+      </x:c>
+      <x:c r="D4" s="65" t="str">
+        <x:v>Período / data de referência</x:v>
+      </x:c>
+      <x:c r="E4" s="65" t="str">
+        <x:v>Tipo da fonte</x:v>
+      </x:c>
+      <x:c r="F4" s="65" t="str">
+        <x:v>Nome da fonte</x:v>
       </x:c>
       <x:c r="G4" s="24" t="str">
         <x:v>URL</x:v>
       </x:c>
-      <x:c r="H4" s="24" t="str">
-        <x:v>Owner</x:v>
-      </x:c>
-      <x:c r="I4" s="24" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
-      <x:c r="J4" s="25" t="str">
-        <x:v>Accessed</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
+      <x:c r="H4" s="65" t="str">
+        <x:v>Responsável</x:v>
+      </x:c>
+      <x:c r="I4" s="65" t="str">
+        <x:v>Notas</x:v>
+      </x:c>
+      <x:c r="J4" s="66" t="str">
+        <x:v>Consulta declarada</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="5" t="str">
-        <x:v>Model scenario</x:v>
+        <x:v>Cenário do modelo</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
         <x:v>Atlas AI Brasil</x:v>
@@ -6523,34 +6561,34 @@
         <x:v>2026-07-23</x:v>
       </x:c>
       <x:c r="E5" s="5" t="str">
-        <x:v>Synthetic</x:v>
+        <x:v>Sintético</x:v>
       </x:c>
       <x:c r="F5" s="5" t="str">
-        <x:v>M1 teaching case</x:v>
+        <x:v>Caso didático M1</x:v>
       </x:c>
       <x:c r="G5" s="5" t="str"/>
       <x:c r="H5" s="5" t="str">
-        <x:v>Learner</x:v>
+        <x:v>Participante</x:v>
       </x:c>
       <x:c r="I5" s="5" t="str">
-        <x:v>Not a real company</x:v>
+        <x:v>Empresa fictícia</x:v>
       </x:c>
       <x:c r="J5" s="5" t="str">
         <x:v>2026-07-23</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
+    <x:row r="6" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A6" s="5" t="str">
-        <x:v>10-K structure</x:v>
+        <x:v>Estrutura de documento 10-K dos EUA</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
-        <x:v>Income statement, balance sheet, cash flow and notes</x:v>
+        <x:v>Demonstração de resultado, balanço, fluxo de caixa e notas</x:v>
       </x:c>
       <x:c r="C6" s="5" t="str">
         <x:v>n/a</x:v>
       </x:c>
       <x:c r="D6" s="5" t="str">
-        <x:v>current</x:v>
+        <x:v>atual</x:v>
       </x:c>
       <x:c r="E6" s="5" t="str">
         <x:v>T0</x:v>
@@ -6562,18 +6600,18 @@
         <x:v>https://www.investor.gov/introduction-investing/getting-started/researching-investments/how-read-10-k</x:v>
       </x:c>
       <x:c r="H6" s="5" t="str">
-        <x:v>Program</x:v>
+        <x:v>Programa</x:v>
       </x:c>
       <x:c r="I6" s="5" t="str">
-        <x:v>Reading source</x:v>
+        <x:v>Fonte de leitura</x:v>
       </x:c>
       <x:c r="J6" s="5" t="str">
         <x:v>2026-07-23</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
+    <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A7" s="5" t="str">
-        <x:v>Real filing case</x:v>
+        <x:v>Caso de documento financeiro real</x:v>
       </x:c>
       <x:c r="B7" s="5" t="str">
         <x:v>Salesforce FY2026 10-K</x:v>
@@ -6594,27 +6632,27 @@
         <x:v>https://www.sec.gov/Archives/edgar/data/1108524/000110852426000060/crm-20260131.htm</x:v>
       </x:c>
       <x:c r="H7" s="5" t="str">
-        <x:v>Program</x:v>
+        <x:v>Programa</x:v>
       </x:c>
       <x:c r="I7" s="5" t="str">
-        <x:v>Used in module, not as model inputs</x:v>
+        <x:v>Usado na aula, não como entrada do modelo</x:v>
       </x:c>
       <x:c r="J7" s="5" t="str">
         <x:v>2026-07-23</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
+    <x:row r="8" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A8" s="5" t="str">
-        <x:v>FX reference</x:v>
+        <x:v>Referência cambial</x:v>
       </x:c>
       <x:c r="B8" s="5" t="str">
-        <x:v>Official exchange-rate resources</x:v>
+        <x:v>Fontes oficiais de câmbio</x:v>
       </x:c>
       <x:c r="C8" s="5" t="str">
-        <x:v>various</x:v>
+        <x:v>diversos</x:v>
       </x:c>
       <x:c r="D8" s="5" t="str">
-        <x:v>current</x:v>
+        <x:v>atual</x:v>
       </x:c>
       <x:c r="E8" s="5" t="str">
         <x:v>T0</x:v>
@@ -6626,10 +6664,10 @@
         <x:v>https://www.bcb.gov.br/estabilidadefinanceira/cambioecapitais</x:v>
       </x:c>
       <x:c r="H8" s="5" t="str">
-        <x:v>Learner</x:v>
+        <x:v>Participante</x:v>
       </x:c>
       <x:c r="I8" s="5" t="str">
-        <x:v>Real execution includes spread/timing</x:v>
+        <x:v>Execução real inclui diferencial cambial e prazos</x:v>
       </x:c>
       <x:c r="J8" s="5" t="str">
         <x:v>2026-07-23</x:v>
